--- a/data/trans_orig/IP18A03-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP18A03-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63230</t>
+          <t>62949</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80315</t>
+          <t>80023</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71594</t>
+          <t>71967</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90411</t>
+          <t>90030</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>139380</t>
+          <t>139724</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>165225</t>
+          <t>165419</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,64%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35230</t>
+          <t>35522</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52315</t>
+          <t>52596</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38586</t>
+          <t>38967</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57403</t>
+          <t>57030</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79317</t>
+          <t>79123</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105162</t>
+          <t>104818</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,86%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>101288</t>
+          <t>101746</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>121605</t>
+          <t>120633</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>105269</t>
+          <t>105865</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>126641</t>
+          <t>126276</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>214002</t>
+          <t>214200</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>241563</t>
+          <t>241693</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>70,0%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43748</t>
+          <t>44720</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64065</t>
+          <t>63607</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53275</t>
+          <t>53640</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>74647</t>
+          <t>74051</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>103706</t>
+          <t>103576</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>131267</t>
+          <t>131069</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,96%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70829</t>
+          <t>70725</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87632</t>
+          <t>87595</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77953</t>
+          <t>77660</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94552</t>
+          <t>94555</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>154482</t>
+          <t>153142</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>177446</t>
+          <t>177134</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,56%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36945</t>
+          <t>36982</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53748</t>
+          <t>53852</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39244</t>
+          <t>39241</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55843</t>
+          <t>56136</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80927</t>
+          <t>81239</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>103891</t>
+          <t>105231</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,73%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100789</t>
+          <t>99660</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123279</t>
+          <t>122699</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106679</t>
+          <t>107131</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127393</t>
+          <t>128493</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>214222</t>
+          <t>212959</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>245686</t>
+          <t>245545</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,68%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69264</t>
+          <t>69844</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>91754</t>
+          <t>92883</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53913</t>
+          <t>52813</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74627</t>
+          <t>74175</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128162</t>
+          <t>128303</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>159626</t>
+          <t>160889</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>43,04%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>356422</t>
+          <t>357395</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>394946</t>
+          <t>395617</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>380118</t>
+          <t>382268</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>422228</t>
+          <t>419985</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>750925</t>
+          <t>748592</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>804747</t>
+          <t>803506</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,75%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203072</t>
+          <t>202401</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>241596</t>
+          <t>240623</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>201786</t>
+          <t>204029</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>243896</t>
+          <t>241746</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>417285</t>
+          <t>418526</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>471107</t>
+          <t>473440</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,74%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>78060</t>
+          <t>78802</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>95904</t>
+          <t>96943</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>79803</t>
+          <t>79181</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>99551</t>
+          <t>99144</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>163059</t>
+          <t>164620</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>191015</t>
+          <t>190715</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,23%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34867</t>
+          <t>33828</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52711</t>
+          <t>51969</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45153</t>
+          <t>45560</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64901</t>
+          <t>65523</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84460</t>
+          <t>84760</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112416</t>
+          <t>110855</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,24%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>123715</t>
+          <t>122405</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>142899</t>
+          <t>142892</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>139893</t>
+          <t>139272</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>160784</t>
+          <t>160120</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>268871</t>
+          <t>269153</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>297945</t>
+          <t>297967</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49835</t>
+          <t>49842</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69019</t>
+          <t>70329</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47723</t>
+          <t>48387</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>68614</t>
+          <t>69235</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>103296</t>
+          <t>103274</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>132370</t>
+          <t>132088</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,92%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85026</t>
+          <t>84931</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>102292</t>
+          <t>102602</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96248</t>
+          <t>96347</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115254</t>
+          <t>114774</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>187150</t>
+          <t>187210</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>213089</t>
+          <t>212772</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,2%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39771</t>
+          <t>39461</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57037</t>
+          <t>57132</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41532</t>
+          <t>42012</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60538</t>
+          <t>60439</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85760</t>
+          <t>86077</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111699</t>
+          <t>111639</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,36%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>108124</t>
+          <t>107694</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130958</t>
+          <t>131665</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110712</t>
+          <t>110586</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>134784</t>
+          <t>134672</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>225590</t>
+          <t>226378</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>260762</t>
+          <t>260036</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,26%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71492</t>
+          <t>70785</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>94326</t>
+          <t>94756</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67452</t>
+          <t>67564</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91524</t>
+          <t>91650</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>143924</t>
+          <t>144650</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>179096</t>
+          <t>178308</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,06%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>413497</t>
+          <t>415593</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>454263</t>
+          <t>454096</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>447890</t>
+          <t>446708</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>490760</t>
+          <t>490247</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>875216</t>
+          <t>874944</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>931656</t>
+          <t>933318</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,62%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>213756</t>
+          <t>213923</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>254522</t>
+          <t>252426</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>221472</t>
+          <t>221985</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>264342</t>
+          <t>265524</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>448595</t>
+          <t>446933</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>505035</t>
+          <t>505307</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,61%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76181</t>
+          <t>76264</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94056</t>
+          <t>93490</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>76982</t>
+          <t>77047</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>96081</t>
+          <t>96384</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>159654</t>
+          <t>159420</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>185525</t>
+          <t>183493</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>70,96%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30684</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48559</t>
+          <t>48476</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37770</t>
+          <t>37467</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56869</t>
+          <t>56804</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73066</t>
+          <t>75098</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98937</t>
+          <t>99171</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>119634</t>
+          <t>119057</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>138995</t>
+          <t>139650</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>132861</t>
+          <t>132386</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>154406</t>
+          <t>154057</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>257640</t>
+          <t>259488</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>287665</t>
+          <t>288654</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,57%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54323</t>
+          <t>53668</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73684</t>
+          <t>74261</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55600</t>
+          <t>55949</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>77145</t>
+          <t>77620</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>115659</t>
+          <t>114670</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>145684</t>
+          <t>143836</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80799</t>
+          <t>79980</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96894</t>
+          <t>97679</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78487</t>
+          <t>77988</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97195</t>
+          <t>97227</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>165482</t>
+          <t>165251</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>189788</t>
+          <t>190240</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,03%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39677</t>
+          <t>38892</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55772</t>
+          <t>56591</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45886</t>
+          <t>45854</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64594</t>
+          <t>65093</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89864</t>
+          <t>89412</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>114170</t>
+          <t>114401</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,91%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106224</t>
+          <t>104603</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127743</t>
+          <t>128288</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105761</t>
+          <t>106327</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128311</t>
+          <t>127675</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>218191</t>
+          <t>218930</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>249511</t>
+          <t>250090</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,23%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64905</t>
+          <t>64360</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>86424</t>
+          <t>88045</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56652</t>
+          <t>57288</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79202</t>
+          <t>78636</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128100</t>
+          <t>127521</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>159420</t>
+          <t>158681</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,02%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>401597</t>
+          <t>402102</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>440376</t>
+          <t>441011</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>415013</t>
+          <t>415971</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>455541</t>
+          <t>454660</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>827832</t>
+          <t>828723</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>884042</t>
+          <t>884751</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,07%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>206901</t>
+          <t>206266</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>245680</t>
+          <t>245175</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>216360</t>
+          <t>217241</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>256888</t>
+          <t>255930</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>435136</t>
+          <t>434427</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>491346</t>
+          <t>490455</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10466</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15871</t>
+          <t>15817</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15380</t>
+          <t>15238</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20757</t>
+          <t>20613</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27975</t>
+          <t>27728</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35586</t>
+          <t>35475</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,62%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6588</t>
+          <t>6714</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10745</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18162</t>
+          <t>18045</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25664</t>
+          <t>25751</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30524</t>
+          <t>30151</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40936</t>
+          <t>41191</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52336</t>
+          <t>52353</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65134</t>
+          <t>64466</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>81,9%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10813</t>
+          <t>10930</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8800</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19212</t>
+          <t>19585</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13577</t>
+          <t>14245</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26375</t>
+          <t>26358</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,49%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15513</t>
+          <t>14954</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22984</t>
+          <t>22814</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23423</t>
+          <t>23247</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29863</t>
+          <t>29925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41312</t>
+          <t>40617</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51407</t>
+          <t>51537</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,98%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10723</t>
+          <t>11282</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1817</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16605</t>
+          <t>17300</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17387</t>
+          <t>17062</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24695</t>
+          <t>24657</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18547</t>
+          <t>18289</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25616</t>
+          <t>25636</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37786</t>
+          <t>37587</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48274</t>
+          <t>47898</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>84,69%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>10987</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9963</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8285</t>
+          <t>8661</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18773</t>
+          <t>18972</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,54%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69996</t>
+          <t>69339</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84020</t>
+          <t>83614</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>96721</t>
+          <t>97109</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111564</t>
+          <t>111974</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>170762</t>
+          <t>170971</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>191593</t>
+          <t>192659</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16294</t>
+          <t>16700</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30318</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20028</t>
+          <t>19618</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34871</t>
+          <t>34483</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40313</t>
+          <t>39247</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61144</t>
+          <t>60935</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP18A03-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP18A03-Habitat-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por diagnóstico y tratamiento en 2007 (tasa de respuesta: 99,78%)</t>
+          <t>Menores según si su última consulta médica fue por diagnóstico y/o tratamiento [en 2023 se preguntan por separado] en 2007 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>81011</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>71629</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>89675</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>62,8%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>55,53%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>69,52%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>72330</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>62949</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>80023</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>64095</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>81072</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>62,6%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>54,48%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>69,26%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>81011</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>71967</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>90030</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>62,8%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>139724</t>
+          <t>141002</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>165419</t>
+          <t>165347</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,61%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>47986</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>39322</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>57368</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>37,2%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>30,48%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>44,47%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>43215</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>35522</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>52596</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>34473</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>51450</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>37,4%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>30,74%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>45,52%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>47986</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>38967</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>57030</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>37,2%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79123</t>
+          <t>79195</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104818</t>
+          <t>103540</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,34%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>128997</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>128997</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>128997</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>115545</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>115545</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>115545</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>128997</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>128997</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>128997</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>116647</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>105305</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>126181</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>64,83%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>58,53%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>70,13%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>111828</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>101746</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>120633</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>101096</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>120095</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>67,63%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>61,53%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>72,96%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>116647</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>105865</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>126276</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>64,83%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>214200</t>
+          <t>214477</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>241693</t>
+          <t>242201</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>70,15%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>63269</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>53735</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>74611</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>35,17%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>29,87%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>41,47%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>53525</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>44720</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>63607</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>45258</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>64257</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>32,37%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>27,04%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>38,47%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>63269</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>53640</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>74051</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>35,17%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>103576</t>
+          <t>103068</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>131069</t>
+          <t>130792</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>179916</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>179916</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>179916</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>165353</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>165353</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>165353</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>179916</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>179916</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>179916</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>86280</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>77564</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>94259</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>64,49%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>57,97%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>70,45%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>79524</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>70725</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>87595</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>70418</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>86887</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>63,83%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>56,77%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>70,31%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>86280</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>77660</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>94555</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>64,49%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>153142</t>
+          <t>152119</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>177134</t>
+          <t>176746</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,41%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>47516</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>39537</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>56232</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>35,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>29,55%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>42,03%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>45053</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>36982</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>53852</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>37690</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>54159</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>36,17%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>29,69%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>43,23%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>47516</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>39241</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>56136</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>35,51%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>81239</t>
+          <t>81627</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>105231</t>
+          <t>106254</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>41,12%</t>
         </is>
       </c>
     </row>
@@ -1640,52 +1640,52 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>133796</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>133796</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>133796</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>124577</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>124577</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>124577</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>133796</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>133796</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>133796</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>117665</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>107928</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>128258</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>64,9%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>59,53%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>70,74%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>111906</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>99660</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>122699</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>100709</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>123294</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>58,12%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>51,76%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>63,73%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>117665</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>107131</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>128493</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>64,9%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>212959</t>
+          <t>212850</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>245545</t>
+          <t>244454</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,39%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>63641</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>53048</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>73378</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>35,1%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>29,26%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>40,47%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>80637</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>69844</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>92883</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>69249</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>91834</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>41,88%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>36,27%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>48,24%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>63641</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>52813</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>74175</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>35,1%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128303</t>
+          <t>129394</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>160889</t>
+          <t>160998</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,07%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>181306</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>181306</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>181306</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>192543</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>192543</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>192543</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>181306</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>181306</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>181306</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>401602</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>381638</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>420087</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>64,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>61,16%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>67,32%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>557</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>375587</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>357395</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>395617</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>355869</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>393637</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>62,81%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>59,76%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>66,15%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>401602</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>382268</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>419985</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>64,36%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>748592</t>
+          <t>750086</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>803506</t>
+          <t>804351</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,82%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>222412</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>203927</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>242376</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>35,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>32,68%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>38,84%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>335</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>222431</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>202401</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>240623</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>204381</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>242149</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>37,19%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>33,85%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>40,24%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>222412</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>204029</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>241746</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>35,64%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>418526</t>
+          <t>417681</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>473440</t>
+          <t>471946</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,62%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>892</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>598018</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>598018</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>598018</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2485,13 +2485,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por diagnóstico y tratamiento en 2012 (tasa de respuesta: 98,75%)</t>
+          <t>Menores según si su última consulta médica fue por diagnóstico y/o tratamiento [en 2023 se preguntan por separado] en 2012 (tasa de respuesta: 98,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>89677</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>79609</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>99723</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>61,97%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>55,02%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>68,92%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>87582</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>78802</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>96943</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>78027</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>96402</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>66,97%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>60,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>74,13%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>89677</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>79181</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>99144</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>61,97%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>164620</t>
+          <t>162243</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>190715</t>
+          <t>189119</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>68,65%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>55027</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>44981</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>65095</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>38,03%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>31,08%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>44,98%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>43189</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>33828</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>51969</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>34369</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>52744</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>33,03%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,87%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>39,74%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>55027</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>45560</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>65523</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>38,03%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84760</t>
+          <t>86356</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110855</t>
+          <t>113232</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>41,1%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>144704</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>144704</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>144704</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>130771</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>130771</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>130771</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>144704</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>144704</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>144704</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>150422</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>139005</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>160728</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>72,14%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>66,67%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>77,09%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>133440</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>122405</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>142892</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>123412</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>143798</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>69,24%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>63,51%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>74,14%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>150422</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>139272</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>160120</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>72,14%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>269153</t>
+          <t>269409</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>297967</t>
+          <t>298888</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,49%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>58085</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>69502</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>27,86%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>22,91%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>33,33%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>59294</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>49842</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>70329</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>48936</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>69322</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>30,76%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>25,86%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>36,49%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>58085</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>48387</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>69235</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>27,86%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>103274</t>
+          <t>102353</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>132088</t>
+          <t>131832</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>208507</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>208507</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>208507</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>192734</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>192734</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>192734</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>208507</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>208507</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>208507</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>105682</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>95450</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>114497</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>67,41%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>60,88%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>73,03%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>94253</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>84931</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>102602</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>84974</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>102915</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>66,35%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>59,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>72,22%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>105682</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>96347</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>114774</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>67,41%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>187210</t>
+          <t>185281</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>212772</t>
+          <t>212442</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,09%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>51104</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>42289</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>61336</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>32,59%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>26,97%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39,12%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>47810</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>39461</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>57132</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>39148</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>57089</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>33,65%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>27,78%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>40,22%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>51104</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>42012</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>60439</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>32,59%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86077</t>
+          <t>86407</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111639</t>
+          <t>113568</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>38,0%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>156786</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>156786</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>156786</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>142063</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>142063</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>142063</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>156786</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>156786</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>156786</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>123060</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>111649</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>134299</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>60,85%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>55,21%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>66,41%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>120403</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>107694</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>131665</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>108657</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>131796</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>59,47%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>53,2%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>65,04%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>123060</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>110586</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>134672</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>60,85%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>226378</t>
+          <t>227379</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>260036</t>
+          <t>260713</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,42%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>79176</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>90587</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>39,15%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>33,59%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>44,79%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>82047</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>70785</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>94756</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>70654</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>93793</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>40,53%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>34,96%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>46,8%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>79176</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>67564</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>91650</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>39,15%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>144650</t>
+          <t>143973</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>178308</t>
+          <t>177307</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,81%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202236</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202236</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202236</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>202450</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>202450</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>202450</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202236</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202236</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202236</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>468840</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>446719</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>489949</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>65,83%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>62,72%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>68,79%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>435678</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>415593</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>454096</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>415703</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>455491</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>65,22%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>62,21%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>67,98%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>468840</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>446708</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>490247</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>65,83%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>874944</t>
+          <t>875273</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>933318</t>
+          <t>933404</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,63%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>243392</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>222283</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>265513</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>34,17%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,21%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>37,28%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>333</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>232341</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>213923</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>252426</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>212528</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>252316</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>34,78%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>32,02%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>37,79%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>243392</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>221985</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>265524</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>34,17%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>446933</t>
+          <t>446847</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>505307</t>
+          <t>504978</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,59%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1012</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>712232</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>712232</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>712232</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>961</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>668019</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>668019</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>668019</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>712232</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>712232</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>712232</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,13 +4432,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por diagnóstico y tratamiento en 2016 (tasa de respuesta: 98,83%)</t>
+          <t>Menores según si su última consulta médica fue por diagnóstico y/o tratamiento [en 2023 se preguntan por separado] en 2016 (tasa de respuesta: 98,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>87351</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>77565</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>97273</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>65,26%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>57,95%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>72,67%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>85224</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>76264</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>93490</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>76278</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>93514</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>68,32%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>61,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>74,95%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>87351</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>77047</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>96384</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>65,26%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>159420</t>
+          <t>159822</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>183493</t>
+          <t>185328</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>71,67%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>46500</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>36578</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>56286</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34,74%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>27,33%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>42,05%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>39516</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>31250</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>48476</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>31226</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>48462</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>31,68%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,05%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>38,86%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>46500</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>37467</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>56804</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>34,74%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75098</t>
+          <t>73263</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99171</t>
+          <t>98769</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,19%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>133851</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>133851</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>133851</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>124740</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>124740</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>124740</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>133851</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>133851</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>133851</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>144106</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>132822</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>156124</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>68,62%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>63,25%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>74,34%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>129615</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>119057</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>139650</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>117899</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>138540</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>67,05%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>61,59%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>72,24%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>144106</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>132386</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>154057</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>68,62%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>259488</t>
+          <t>258719</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>288654</t>
+          <t>287325</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,24%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>65900</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>53882</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>77184</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>31,38%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>25,66%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>36,75%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>63703</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>53668</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>74261</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>54778</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>75419</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>32,95%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>27,76%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>38,41%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>65900</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>55949</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>77620</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>31,38%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>114670</t>
+          <t>115999</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>143836</t>
+          <t>144605</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,85%</t>
         </is>
       </c>
     </row>
@@ -5191,52 +5191,52 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>210006</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>210006</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>210006</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>193318</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>193318</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>193318</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>210006</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>210006</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>210006</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>87715</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>77916</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>96470</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>61,3%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>54,46%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>67,42%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>89039</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>79980</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>97679</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>79874</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>96806</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>65,2%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>58,56%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>71,52%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>87715</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>77988</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>97227</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>61,3%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>165251</t>
+          <t>163225</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>190240</t>
+          <t>189191</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>67,65%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>55366</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>46611</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>65165</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>38,7%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>32,58%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>45,54%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>47532</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>38892</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>56591</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>39765</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>56697</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>34,8%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>28,48%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>41,44%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>55366</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>45854</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>65093</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>38,7%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89412</t>
+          <t>90461</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>114401</t>
+          <t>116427</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,63%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>143081</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>143081</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>143081</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>136571</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>136571</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>136571</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>143081</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>143081</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>143081</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>116819</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>106200</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>128080</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>63,16%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>57,42%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>69,25%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>117278</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>104603</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>128288</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>106154</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>128357</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>60,88%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>54,3%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>66,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>116819</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>106327</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>127675</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>63,16%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>218930</t>
+          <t>218353</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>250090</t>
+          <t>248969</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>65,93%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>68144</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>56883</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>78763</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>36,84%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>30,75%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>42,58%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>75370</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>64360</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>88045</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>64291</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>86494</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>39,12%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>33,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>45,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>68144</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>57288</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>78636</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>36,84%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>127521</t>
+          <t>128642</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>158681</t>
+          <t>159258</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,18%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>184963</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>184963</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>184963</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>192648</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>192648</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>192648</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>184963</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>184963</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>184963</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>435992</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>415725</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>456400</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>64,89%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>61,87%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>67,93%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>629</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>421157</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>402102</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>441011</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>401981</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>440299</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>65,07%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>62,12%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>68,13%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>435992</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>415971</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>454660</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>64,89%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>828723</t>
+          <t>829481</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>884751</t>
+          <t>885929</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,16%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>235909</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>215501</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>256176</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>35,11%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>32,07%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>38,13%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>345</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>226120</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>206266</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>245175</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>206978</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>245296</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>34,93%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>31,87%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>37,88%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>235909</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>217241</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>255930</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>35,11%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>434427</t>
+          <t>433249</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>490455</t>
+          <t>489697</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,12%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>671901</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>671901</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>671901</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>974</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>647277</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>647277</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>647277</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>961</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>671901</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>671901</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>671901</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6379,13 +6379,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por diagnóstico y tratamiento en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si su última consulta médica fue por diagnóstico y/o tratamiento [en 2023 se preguntan por separado] en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17158</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13786</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19074</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>85,6%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>68,78%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>95,17%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13769</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10340</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15817</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>80,74%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>60,63%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>92,75%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>18549</t>
+          <t>14051</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15238</t>
+          <t>10747</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20613</t>
+          <t>15969</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>32318</t>
+          <t>31209</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27728</t>
+          <t>26957</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35475</t>
+          <t>34085</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,66%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6257</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14,4%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>31,22%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3285</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1237</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6714</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>19,26%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7,25%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>39,37%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6402</t>
+          <t>5978</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10992</t>
+          <t>10230</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20043</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20043</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20043</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>17054</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17054</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17054</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21666</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21666</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21666</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>32673</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>26949</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>36989</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>71,98%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>59,37%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>81,49%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>22533</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>18045</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>25751</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>77,77%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>62,28%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>88,87%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36171</t>
+          <t>20265</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30151</t>
+          <t>15395</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41191</t>
+          <t>23389</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>58704</t>
+          <t>52938</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52353</t>
+          <t>46573</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64466</t>
+          <t>58548</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>80,93%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12720</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8404</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18444</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>28,02%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>18,51%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>40,63%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6442</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3224</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10930</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>22,23%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,13%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>37,72%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13565</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19585</t>
+          <t>11554</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>20007</t>
+          <t>19404</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14245</t>
+          <t>13794</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26358</t>
+          <t>25769</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>35,62%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45393</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45393</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>45393</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>28975</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>28975</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>28975</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49736</t>
+          <t>26949</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49736</t>
+          <t>26949</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49736</t>
+          <t>26949</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>78711</t>
+          <t>72342</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>78711</t>
+          <t>72342</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>78711</t>
+          <t>72342</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>26226</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21984</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28703</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>86,89%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>72,84%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>95,1%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>19580</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14954</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22814</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>74,63%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>57,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>86,96%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>27476</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23247</t>
+          <t>12839</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29925</t>
+          <t>19987</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>47057</t>
+          <t>42996</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40617</t>
+          <t>36603</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51537</t>
+          <t>47600</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,31%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3957</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8199</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>13,11%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>27,16%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>6656</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3422</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>11282</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>25,37%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>13,04%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>43,0%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>10879</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>10860</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17300</t>
+          <t>17298</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>30183</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>30183</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>30183</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>26236</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>26236</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>26236</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>57917</t>
+          <t>53901</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>57917</t>
+          <t>53901</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57917</t>
+          <t>53901</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21451</t>
+          <t>20386</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17062</t>
+          <t>16348</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24657</t>
+          <t>23292</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22397</t>
+          <t>21076</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18289</t>
+          <t>16921</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25636</t>
+          <t>24387</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>43848</t>
+          <t>41462</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37587</t>
+          <t>35751</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47898</t>
+          <t>45897</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>85,3%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5717</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2811</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9755</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>21,9%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>10,77%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>37,37%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>6598</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3392</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10987</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>23,52%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12,09%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>39,17%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>10780</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>12711</t>
+          <t>12342</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8661</t>
+          <t>7907</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18972</t>
+          <t>18053</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,55%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>26103</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>26103</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>26103</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>28049</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>28049</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>28049</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>27701</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>27701</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>27701</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>56559</t>
+          <t>53804</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>56559</t>
+          <t>53804</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>56559</t>
+          <t>53804</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>96443</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>88848</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>103108</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>79,23%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>72,99%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>84,71%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>77333</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>69339</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>83614</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>77,09%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>69,12%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>83,35%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>104593</t>
+          <t>72162</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>97109</t>
+          <t>64389</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111974</t>
+          <t>78663</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>181926</t>
+          <t>168605</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>170971</t>
+          <t>157965</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>192659</t>
+          <t>178217</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,04%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>25279</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18614</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>32874</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>20,77%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>15,29%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>27,01%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>22981</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>16700</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>30975</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>22,91%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>16,65%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>30,88%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>26999</t>
+          <t>23350</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19618</t>
+          <t>16849</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34483</t>
+          <t>31123</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>49980</t>
+          <t>48629</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39247</t>
+          <t>39017</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60935</t>
+          <t>59269</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
